--- a/CodeSystem-location-type-cs.xlsx
+++ b/CodeSystem-location-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-29T10:31:38+00:00</t>
+    <t>2025-05-30T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -135,397 +135,397 @@
     <t>1</t>
   </si>
   <si>
-    <t>toi</t>
+    <t>211</t>
   </si>
   <si>
     <t>Toimistotila</t>
   </si>
   <si>
-    <t>toe</t>
+    <t>2112</t>
   </si>
   <si>
     <t>Toimistotila, erikoisvarustus</t>
   </si>
   <si>
-    <t>kok</t>
+    <t>214</t>
   </si>
   <si>
     <t>Kokoustila</t>
   </si>
   <si>
-    <t>mot</t>
+    <t>215</t>
   </si>
   <si>
     <t>Monitoimityötila</t>
   </si>
   <si>
-    <t>lii</t>
+    <t>22</t>
   </si>
   <si>
     <t>Liiketila</t>
   </si>
   <si>
-    <t>opt</t>
+    <t>31</t>
   </si>
   <si>
     <t>Opetustila tai luentosali</t>
   </si>
   <si>
-    <t>mtp</t>
+    <t>3249</t>
   </si>
   <si>
     <t>Muu opetus- tai terapiatila</t>
   </si>
   <si>
-    <t>lab</t>
+    <t>362</t>
   </si>
   <si>
     <t>Laboratorio</t>
   </si>
   <si>
-    <t>puh</t>
+    <t>3651</t>
   </si>
   <si>
     <t>Puhdastila</t>
   </si>
   <si>
-    <t>olo</t>
+    <t>366</t>
   </si>
   <si>
     <t>Olosuhdehuone</t>
   </si>
   <si>
-    <t>rhy</t>
+    <t>371</t>
   </si>
   <si>
     <t>Ryhmätila</t>
   </si>
   <si>
-    <t>lei</t>
+    <t>441</t>
   </si>
   <si>
     <t>Leikkaussali</t>
   </si>
   <si>
-    <t>syn</t>
+    <t>4411</t>
   </si>
   <si>
     <t>Synnytyssali</t>
   </si>
   <si>
-    <t>pot</t>
+    <t>442</t>
   </si>
   <si>
     <t>Potilashuone</t>
   </si>
   <si>
-    <t>eri</t>
+    <t>4421</t>
   </si>
   <si>
     <t>Eristyshuone</t>
   </si>
   <si>
-    <t>teh</t>
+    <t>4422</t>
   </si>
   <si>
     <t>Tehohoitotila</t>
   </si>
   <si>
-    <t>kap</t>
+    <t>443</t>
   </si>
   <si>
     <t>Kappeli tai jäähyväishuone</t>
   </si>
   <si>
-    <t>tph</t>
+    <t>444</t>
   </si>
   <si>
     <t>Toimenpidehuone</t>
   </si>
   <si>
-    <t>vas</t>
+    <t>4441</t>
   </si>
   <si>
     <t>Vastaanottohuone</t>
   </si>
   <si>
-    <t>vak</t>
+    <t>44411</t>
   </si>
   <si>
     <t>Vastaanottohuone, kevyt</t>
   </si>
   <si>
-    <t>vae</t>
+    <t>44412</t>
   </si>
   <si>
     <t>Vastaanottohuone, erikoisvarustus</t>
   </si>
   <si>
-    <t>kuv</t>
+    <t>4443</t>
   </si>
   <si>
     <t>Kuvantamishuone</t>
   </si>
   <si>
-    <t>kve</t>
+    <t>4445</t>
   </si>
   <si>
     <t>Kuvantamishuone, erikoisvarustus</t>
   </si>
   <si>
-    <t>val</t>
+    <t>4451</t>
   </si>
   <si>
     <t>Valvonta- tai tarkkailutila</t>
   </si>
   <si>
-    <t>her</t>
+    <t>4454</t>
   </si>
   <si>
     <t>Heräämö</t>
   </si>
   <si>
-    <t>vai</t>
+    <t>446</t>
   </si>
   <si>
     <t>Vainajien säilytystila</t>
   </si>
   <si>
-    <t>obd</t>
+    <t>447</t>
   </si>
   <si>
     <t>Obduktio- tai dissektiotila</t>
   </si>
   <si>
-    <t>whs</t>
+    <t>448</t>
   </si>
   <si>
     <t>Välinehuoltotila</t>
   </si>
   <si>
-    <t>lib</t>
+    <t>4615</t>
   </si>
   <si>
     <t>Kirjasto</t>
   </si>
   <si>
-    <t>gym</t>
+    <t>471</t>
   </si>
   <si>
     <t>Liikuntasali</t>
   </si>
   <si>
-    <t>fit</t>
+    <t>472</t>
   </si>
   <si>
     <t>Kuntosali</t>
   </si>
   <si>
-    <t>res</t>
+    <t>4911</t>
   </si>
   <si>
     <t>Pelastustoimen laitehuoltotila</t>
   </si>
   <si>
-    <t>sto</t>
+    <t>521</t>
   </si>
   <si>
     <t>Varastotila</t>
   </si>
   <si>
-    <t>stc</t>
+    <t>5292</t>
   </si>
   <si>
     <t>Varastotila, kylmä</t>
   </si>
   <si>
-    <t>ste</t>
+    <t>5293</t>
   </si>
   <si>
     <t>Varastotila, erikoisvarustus</t>
   </si>
   <si>
-    <t>arc</t>
+    <t>531</t>
   </si>
   <si>
     <t>Arkistotila</t>
   </si>
   <si>
-    <t>gar</t>
+    <t>552</t>
   </si>
   <si>
     <t>Auto- tai kalustohalli, lämmin</t>
   </si>
   <si>
-    <t>was</t>
+    <t>555</t>
   </si>
   <si>
     <t>Pesuhalli</t>
   </si>
   <si>
-    <t>din</t>
+    <t>63</t>
   </si>
   <si>
     <t>Ruokasali</t>
   </si>
   <si>
-    <t>kit</t>
+    <t>642</t>
   </si>
   <si>
     <t>Keittiö</t>
   </si>
   <si>
-    <t>ser</t>
+    <t>645</t>
   </si>
   <si>
     <t>Jakelukeittiö tai palvelukeittiö</t>
   </si>
   <si>
-    <t>ref</t>
+    <t>651</t>
   </si>
   <si>
     <t>Kylmiö</t>
   </si>
   <si>
-    <t>fre</t>
+    <t>652</t>
   </si>
   <si>
     <t>Pakastehuone</t>
   </si>
   <si>
-    <t>cha</t>
+    <t>71</t>
   </si>
   <si>
     <t>Pukutila</t>
   </si>
   <si>
-    <t>bat</t>
+    <t>72</t>
   </si>
   <si>
     <t>Pesutila</t>
   </si>
   <si>
-    <t>wc</t>
+    <t>73</t>
   </si>
   <si>
     <t>WC-tila</t>
   </si>
   <si>
-    <t>sau</t>
+    <t>74</t>
   </si>
   <si>
     <t>Sauna</t>
   </si>
   <si>
-    <t>brk</t>
+    <t>751</t>
   </si>
   <si>
     <t>Taukotila</t>
   </si>
   <si>
-    <t>lou</t>
+    <t>752</t>
   </si>
   <si>
     <t>Oleskelutila</t>
   </si>
   <si>
-    <t>rea</t>
+    <t>753</t>
   </si>
   <si>
     <t>Valmiushuone</t>
   </si>
   <si>
-    <t>she</t>
+    <t>81</t>
   </si>
   <si>
     <t>Väestönsuojatila</t>
   </si>
   <si>
-    <t>ent</t>
+    <t>83</t>
   </si>
   <si>
     <t>Sisäänkäyntitila</t>
   </si>
   <si>
-    <t>lob</t>
+    <t>832</t>
   </si>
   <si>
     <t>Aula tai odotustila</t>
   </si>
   <si>
-    <t>cln</t>
+    <t>86</t>
   </si>
   <si>
     <t>Siivous- tai huoltotila</t>
   </si>
   <si>
-    <t>tex</t>
+    <t>865</t>
   </si>
   <si>
     <t>Vaate- tai tekstiilihuoltotila</t>
   </si>
   <si>
-    <t>mnt</t>
+    <t>866</t>
   </si>
   <si>
     <t>Teknisen huollon tila</t>
   </si>
   <si>
-    <t>wasd</t>
+    <t>87</t>
   </si>
   <si>
     <t>Jätehuoltotila</t>
   </si>
   <si>
-    <t>cor</t>
+    <t>91</t>
   </si>
   <si>
     <t>Käytävä (jakava liikenne)</t>
   </si>
   <si>
-    <t>isl</t>
+    <t>911</t>
   </si>
   <si>
     <t>Sulkutila</t>
   </si>
   <si>
-    <t>log</t>
+    <t>912</t>
   </si>
   <si>
     <t>Logistiikka- tai terminaalitila</t>
   </si>
   <si>
-    <t>sta</t>
+    <t>921</t>
   </si>
   <si>
     <t>Porrashuone (osastoiva liikenne)</t>
   </si>
   <si>
-    <t>tfn</t>
+    <t>94</t>
   </si>
   <si>
     <t>Tekninen tila</t>
   </si>
   <si>
-    <t>tfne</t>
+    <t>941</t>
   </si>
   <si>
     <t>Tekninen tila, erikoisvarustus</t>
   </si>
   <si>
-    <t>sup</t>
+    <t>942</t>
   </si>
   <si>
     <t>Tekninen aputila</t>
   </si>
   <si>
-    <t>raw</t>
+    <t>991</t>
   </si>
   <si>
     <t>Raakatila</t>
   </si>
   <si>
-    <t>ele</t>
+    <t>9911</t>
   </si>
   <si>
     <t>Hissi</t>

--- a/CodeSystem-location-type-cs.xlsx
+++ b/CodeSystem-location-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T11:48:20+00:00</t>
+    <t>2025-05-30T11:53:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-location-type-cs.xlsx
+++ b/CodeSystem-location-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T11:53:21+00:00</t>
+    <t>2025-05-30T12:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
